--- a/test_data/Test_Execution_Commands.xlsx
+++ b/test_data/Test_Execution_Commands.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Test Commands" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Commands'!$A$1:$B$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Commands'!$A$1:$B$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_pqme_encounter_creation_with_interpreter.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_pqme_encounter_creation_with_interpreter.py" --headed -v -s</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_pqme_encounter_creation_without_interpreter.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_pqme_encounter_creation_without_interpreter.py" --headed -v -s</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_pqmed_encounter_creation_with_interpreter.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_pqmed_encounter_creation_with_interpreter.py" --headed -v -s</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_pqmed_encounter_creation_without_interpreter.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_pqmed_encounter_creation_without_interpreter.py" --headed -v -s</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_pqmer_encounter_creation_with_interpreter.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_pqmer_encounter_creation_with_interpreter.py" --headed -v -s</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_pqmer_encounter_creation_without_interpreter.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_pqmer_encounter_creation_without_interpreter.py" --headed -v -s</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_pqmes_encounter_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_pqmes_encounter_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
@@ -535,264 +535,276 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\Encounter Creation\test_reflex_pqmes_encounter_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/Encounter Creation/test_reflex_pqmes_encounter_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Case Manager Phone Number Update and Validation</t>
+          <t>PQME History Details Validation</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_case_manager_phone_update.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/History/test_pqme_history_details_validation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Create Encounter Test Data Workbook Uses Two Level Headers</t>
+          <t>Case Manager Phone Number Update and Validation</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_create_encounter_test_data_workbook_uses_two_level_headers" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_case_manager_phone_update.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Read Encounter Test Data Groups Repeated Field Names By Section</t>
+          <t>Create Encounter Test Data Workbook Uses Two Level Headers</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_read_encounter_test_data_groups_repeated_field_names_by_section" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_create_encounter_test_data_workbook_uses_two_level_headers" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Read Encounter Test Data Supports Custom Sheet Name</t>
+          <t>Read Encounter Test Data Groups Repeated Field Names By Section</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_read_encounter_test_data_supports_custom_sheet_name" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_read_encounter_test_data_groups_repeated_field_names_by_section" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Read Encounter Test Data Formats Date Fields As Mm Dd Yyyy</t>
+          <t>Read Encounter Test Data Supports Custom Sheet Name</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_read_encounter_test_data_formats_date_fields_as_mm_dd_yyyy" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_read_encounter_test_data_supports_custom_sheet_name" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Format Encounter Datetime Value Requires Mm Dd Yyyy Date Output</t>
+          <t>Read Encounter Test Data Formats Date Fields As Mm Dd Yyyy</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_format_encounter_datetime_value_requires_mm_dd_yyyy_date_output" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_read_encounter_test_data_formats_date_fields_as_mm_dd_yyyy" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Format Encounter Date Value Handles Blank Optional Dates</t>
+          <t>Format Encounter Datetime Value Requires Mm Dd Yyyy Date Output</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_format_encounter_date_value_handles_blank_optional_dates" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_format_encounter_datetime_value_requires_mm_dd_yyyy_date_output" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Format Encounter Date Value Rejects Unrecognized Date Text</t>
+          <t>Format Encounter Date Value Handles Blank Optional Dates</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_format_encounter_date_value_rejects_unrecognized_date_text" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_format_encounter_date_value_handles_blank_optional_dates" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Create Encounter Workbook With Interpreter Details</t>
+          <t>Format Encounter Date Value Rejects Unrecognized Date Text</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_encounter_test_data.py::test_create_encounter_workbook_with_interpreter_details" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_format_encounter_date_value_rejects_unrecognized_date_text" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Get Test Data Filters Enabled Create Rows</t>
+          <t>Create Encounter Workbook With Interpreter Details</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_excel_reader.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_encounter_test_data.py::test_create_encounter_workbook_with_interpreter_details" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Super Admin Login</t>
+          <t>Get Test Data Filters Enabled Create Rows</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\test_super_admin_login.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_excel_reader.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Creation of Case Manager and Login Validation</t>
+          <t>Super Admin Login</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_case_manager_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/test_super_admin_login.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Creation of Editor and Login Validation</t>
+          <t>Creation of Case Manager and Login Validation</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_editor_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_case_manager_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Creation of Editor Manager and Login Validation</t>
+          <t>Creation of Editor and Login Validation</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_editor_manager_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_editor_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Creation of Historian and Login Validation</t>
+          <t>Creation of Editor Manager and Login Validation</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_historian_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_editor_manager_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Creation of Historian Manager and Login Validation</t>
+          <t>Creation of Historian and Login Validation</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_historian_manager_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_historian_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Creation of Medical Assistant and Login Validation</t>
+          <t>Creation of Historian Manager and Login Validation</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_medical_assistant_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_historian_manager_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Creation of Medical Assistant Manager and Login Validation</t>
+          <t>Creation of Medical Assistant and Login Validation</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_medical_assistant_manager_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_medical_assistant_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Creation of Record Reviewer and Login Validation</t>
+          <t>Creation of Medical Assistant Manager and Login Validation</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_record_reviewer_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_medical_assistant_manager_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Creation of Record Reviewer Manager and Login Validation</t>
+          <t>Creation of Record Reviewer and Login Validation</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_record_reviewer_manager_creation.py" --headed -v -s</t>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_record_reviewer_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>Creation of Record Reviewer Manager and Login Validation</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_record_reviewer_manager_creation.py" --headed -v -s</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Creation of Report Finalizer and Login Validation</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>.\.venv\Scripts\python.exe -m pytest "tests\User Creation\test_report_finalizer_creation.py" --headed -v -s</t>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>./.venv/Scripts/python.exe -m pytest "tests/User Creation/test_report_finalizer_creation.py" --headed -v -s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B30"/>
+  <autoFilter ref="A1:B31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>